--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2168,6 +2168,38 @@
         <v>207.6</v>
       </c>
     </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B55" s="1" t="n">
+        <v>46278</v>
+      </c>
+      <c r="C55" t="n">
+        <v>209.8</v>
+      </c>
+      <c r="D55" t="n">
+        <v>218.6</v>
+      </c>
+      <c r="E55" t="n">
+        <v>209.6</v>
+      </c>
+      <c r="F55" t="n">
+        <v>211.2</v>
+      </c>
+      <c r="G55" t="n">
+        <v>206.5</v>
+      </c>
+      <c r="H55" t="n">
+        <v>209.9</v>
+      </c>
+      <c r="I55" t="n">
+        <v>218.3</v>
+      </c>
+      <c r="J55" t="n">
+        <v>214.7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J55"/>
+  <dimension ref="A1:J56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2200,6 +2200,38 @@
         <v>214.7</v>
       </c>
     </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B56" s="1" t="n">
+        <v>46285</v>
+      </c>
+      <c r="C56" t="n">
+        <v>228</v>
+      </c>
+      <c r="D56" t="n">
+        <v>237.1</v>
+      </c>
+      <c r="E56" t="n">
+        <v>224.9</v>
+      </c>
+      <c r="F56" t="n">
+        <v>227.2</v>
+      </c>
+      <c r="G56" t="n">
+        <v>222.4</v>
+      </c>
+      <c r="H56" t="n">
+        <v>225.4</v>
+      </c>
+      <c r="I56" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="J56" t="n">
+        <v>232.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J56"/>
+  <dimension ref="A1:J57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2232,6 +2232,38 @@
         <v>232.2</v>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B57" s="1" t="n">
+        <v>46292</v>
+      </c>
+      <c r="C57" t="n">
+        <v>238.2</v>
+      </c>
+      <c r="D57" t="n">
+        <v>248.2</v>
+      </c>
+      <c r="E57" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="F57" t="n">
+        <v>237.7</v>
+      </c>
+      <c r="G57" t="n">
+        <v>233.5</v>
+      </c>
+      <c r="H57" t="n">
+        <v>232.7</v>
+      </c>
+      <c r="I57" t="n">
+        <v>244.9</v>
+      </c>
+      <c r="J57" t="n">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J57"/>
+  <dimension ref="A1:J58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2264,6 +2264,38 @@
         <v>244</v>
       </c>
     </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B58" s="1" t="n">
+        <v>46299</v>
+      </c>
+      <c r="C58" t="n">
+        <v>237</v>
+      </c>
+      <c r="D58" t="n">
+        <v>244.9</v>
+      </c>
+      <c r="E58" t="n">
+        <v>235</v>
+      </c>
+      <c r="F58" t="n">
+        <v>237.1</v>
+      </c>
+      <c r="G58" t="n">
+        <v>232.9</v>
+      </c>
+      <c r="H58" t="n">
+        <v>232.8</v>
+      </c>
+      <c r="I58" t="n">
+        <v>245.2</v>
+      </c>
+      <c r="J58" t="n">
+        <v>244</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J58"/>
+  <dimension ref="A1:J59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2296,6 +2296,38 @@
         <v>244</v>
       </c>
     </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B59" s="1" t="n">
+        <v>46306</v>
+      </c>
+      <c r="C59" t="n">
+        <v>239.5</v>
+      </c>
+      <c r="D59" t="n">
+        <v>244.7</v>
+      </c>
+      <c r="E59" t="n">
+        <v>240.4</v>
+      </c>
+      <c r="F59" t="n">
+        <v>238.6</v>
+      </c>
+      <c r="G59" t="n">
+        <v>235.8</v>
+      </c>
+      <c r="H59" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="I59" t="n">
+        <v>246.8</v>
+      </c>
+      <c r="J59" t="n">
+        <v>249.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J59"/>
+  <dimension ref="A1:J60"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2328,6 +2328,38 @@
         <v>249.2</v>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B60" s="1" t="n">
+        <v>46313</v>
+      </c>
+      <c r="C60" t="n">
+        <v>241.3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="E60" t="n">
+        <v>241.7</v>
+      </c>
+      <c r="F60" t="n">
+        <v>239.9</v>
+      </c>
+      <c r="G60" t="n">
+        <v>236.8</v>
+      </c>
+      <c r="H60" t="n">
+        <v>238.4</v>
+      </c>
+      <c r="I60" t="n">
+        <v>249</v>
+      </c>
+      <c r="J60" t="n">
+        <v>250</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/petrol_weekly_prices.xlsx
+++ b/data/petrol_weekly_prices.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J60"/>
+  <dimension ref="A1:J61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2360,6 +2360,38 @@
         <v>250</v>
       </c>
     </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B61" s="1" t="n">
+        <v>46320</v>
+      </c>
+      <c r="C61" t="n">
+        <v>237.9</v>
+      </c>
+      <c r="D61" t="n">
+        <v>246</v>
+      </c>
+      <c r="E61" t="n">
+        <v>236.5</v>
+      </c>
+      <c r="F61" t="n">
+        <v>237.3</v>
+      </c>
+      <c r="G61" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="H61" t="n">
+        <v>230.1</v>
+      </c>
+      <c r="I61" t="n">
+        <v>246.3</v>
+      </c>
+      <c r="J61" t="n">
+        <v>246.8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
